--- a/report_20260624.xlsx
+++ b/report_20260624.xlsx
@@ -3633,7 +3633,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>0.078</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr"/>
@@ -4007,17 +4007,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>CLDN.L</t>
+          <t>VOF.L</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Caledonia Investments</t>
+          <t>VinaCapital Vietnam Opportunity</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>RECENT_SELLOFF</t>
+          <t>BASE_QUIET</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -4032,26 +4032,26 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.2797505939134894</v>
+        <v>0.3349769753593573</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
           <t>0.044</t>
         </is>
       </c>
-      <c r="J14" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
+      <c r="K14" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="L14" s="6" t="inlineStr"/>
       <c r="M14" s="3" t="n"/>
     </row>
@@ -4107,41 +4107,41 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>VOF.L</t>
+          <t>RMII.L</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>VinaCapital Vietnam Opportunity</t>
+          <t>RM Infrastructure Income</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>BASE_QUIET</t>
+          <t>BASE_DECLINING</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>DCM_ACTIVE</t>
+          <t>WIND_DOWN_LIKELY</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>LISTED_CLEAN</t>
+          <t>DEBT_AMORTISING</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
-        <v>0.3349769753593573</v>
+        <v>0.2229478735228767</v>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="J16" s="6" t="inlineStr"/>
       <c r="K16" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16" s="6" t="inlineStr"/>
       <c r="M16" s="3" t="n"/>
@@ -4158,51 +4158,51 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>RMII.L</t>
+          <t>CLDN.L</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>RM Infrastructure Income</t>
+          <t>Caledonia Investments</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>BASE_DECLINING</t>
+          <t>RECENT_SELLOFF</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>WIND_DOWN_LIKELY</t>
+          <t>DCM_ACTIVE</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>DEBT_AMORTISING</t>
+          <t>LISTED_CLEAN</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="H17" s="7" t="n">
-        <v>0.2229478735228767</v>
+        <v>0.2797505939134894</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>0.039</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr"/>
-      <c r="K17" s="7" t="n">
-        <v>2</v>
-      </c>
+          <t>0.041</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" s="6" t="inlineStr"/>
       <c r="L17" s="6" t="inlineStr"/>
       <c r="M17" s="3" t="n"/>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="H18" s="7" t="n">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>0.041</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr"/>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>0.036</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr"/>
@@ -4666,12 +4666,12 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>SEQI.L</t>
+          <t>TFIF.L</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sequoia Economic Infrastructure </t>
+          <t>TwentyFour Income Fund</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>DCM_ACTIVE</t>
+          <t>STRUCTURAL_DISCOUNT</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -4691,25 +4691,23 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="H27" s="7" t="n">
-        <v>0.1765075585930554</v>
+        <v>0</v>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
           <t>0.033</t>
         </is>
       </c>
-      <c r="J27" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="J27" s="6" t="inlineStr"/>
       <c r="K27" s="6" t="inlineStr"/>
       <c r="L27" s="6" t="inlineStr"/>
       <c r="M27" s="3" t="n"/>
@@ -4717,12 +4715,12 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>TFIF.L</t>
+          <t>SEQI.L</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>TwentyFour Income Fund</t>
+          <t xml:space="preserve">Sequoia Economic Infrastructure </t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -4732,7 +4730,7 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>STRUCTURAL_DISCOUNT</t>
+          <t>DCM_ACTIVE</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -4742,23 +4740,25 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="H28" s="7" t="n">
-        <v>0</v>
+        <v>0.1765075585930554</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
           <t>0.033</t>
         </is>
       </c>
-      <c r="J28" s="6" t="inlineStr"/>
+      <c r="J28" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="K28" s="6" t="inlineStr"/>
       <c r="L28" s="6" t="inlineStr"/>
       <c r="M28" s="3" t="n"/>
@@ -4868,17 +4868,17 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>ALW.L</t>
+          <t>GSF.L</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Alliance Witan</t>
+          <t>Gore Street Energy Storage</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>BASE_ABSORBING</t>
+          <t>BASE_QUIET</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -4888,46 +4888,50 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>LISTED_CLEAN</t>
+          <t>RENEWABLES_DCF</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="H31" s="7" t="n">
-        <v>0.1372526550239795</v>
+        <v>0.3199999999999999</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
           <t>0.031</t>
         </is>
       </c>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="J31" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="L31" s="6" t="inlineStr"/>
       <c r="M31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>GSF.L</t>
+          <t>ALW.L</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Gore Street Energy Storage</t>
+          <t>Alliance Witan</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>BASE_QUIET</t>
+          <t>BASE_ABSORBING</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -4937,33 +4941,29 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>RENEWABLES_DCF</t>
+          <t>LISTED_CLEAN</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="H32" s="7" t="n">
-        <v>0.3199999999999999</v>
+        <v>0.1372526550239795</v>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
           <t>0.031</t>
         </is>
       </c>
-      <c r="J32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="J32" s="6" t="inlineStr"/>
+      <c r="K32" s="6" t="inlineStr"/>
       <c r="L32" s="6" t="inlineStr"/>
       <c r="M32" s="3" t="n"/>
     </row>
@@ -5019,12 +5019,12 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>CVCG.L</t>
+          <t>CTHT.L</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>CVC Income &amp; Growth</t>
+          <t>CT Healthcare Trust</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -5034,46 +5034,50 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>STRUCTURAL_DISCOUNT</t>
+          <t>WIND_DOWN_LIKELY</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>DEBT_AMORTISING</t>
+          <t>LISTED_CLEAN</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="H34" s="7" t="n">
-        <v>0.009422988528750899</v>
+        <v>0.5229266517099029</v>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
           <t>0.030</t>
         </is>
       </c>
-      <c r="J34" s="6" t="inlineStr"/>
-      <c r="K34" s="6" t="inlineStr"/>
+      <c r="J34" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K34" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="L34" s="6" t="inlineStr"/>
       <c r="M34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>CTHT.L</t>
+          <t>CVCG.L</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>CT Healthcare Trust</t>
+          <t>CVC Income &amp; Growth</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -5083,38 +5087,34 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>WIND_DOWN_LIKELY</t>
+          <t>STRUCTURAL_DISCOUNT</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>LISTED_CLEAN</t>
+          <t>DEBT_AMORTISING</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="H35" s="7" t="n">
-        <v>0.5229266517099029</v>
+        <v>0.009422988528750899</v>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>0.029</t>
-        </is>
-      </c>
-      <c r="J35" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>1</v>
-      </c>
+          <t>0.030</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr"/>
+      <c r="K35" s="6" t="inlineStr"/>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="3" t="n"/>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="H38" s="7" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="H50" s="7" t="n">
@@ -5923,12 +5923,12 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>SYNC.L</t>
+          <t>OCI.L</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Syncona</t>
+          <t>Oakley Capital Investments</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -5943,47 +5943,43 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>LISTED_CLEAN</t>
+          <t>PRIVATE_EQUITY</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="H52" s="7" t="n">
-        <v>0.0799999999999999</v>
+        <v>0.2844662934286136</v>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>0.017</t>
-        </is>
-      </c>
-      <c r="J52" s="7" t="n">
+          <t>0.018</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr"/>
+      <c r="K52" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="K52" s="6" t="inlineStr"/>
-      <c r="L52" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="L52" s="6" t="inlineStr"/>
       <c r="M52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>OCI.L</t>
+          <t>SYNC.L</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Oakley Capital Investments</t>
+          <t>Syncona</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -5998,32 +5994,36 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>PRIVATE_EQUITY</t>
+          <t>LISTED_CLEAN</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="H53" s="7" t="n">
-        <v>0.2844662934286136</v>
+        <v>0.0799999999999999</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
           <t>0.017</t>
         </is>
       </c>
-      <c r="J53" s="6" t="inlineStr"/>
-      <c r="K53" s="7" t="n">
+      <c r="J53" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="L53" s="6" t="inlineStr"/>
+      <c r="K53" s="6" t="inlineStr"/>
+      <c r="L53" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="M53" s="3" t="n"/>
     </row>
     <row r="54">
@@ -6331,12 +6331,12 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>WWH.L</t>
+          <t>JEGI.L</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Worldwide Healthcare Trust</t>
+          <t>JPMorgan European Growth &amp; Incom</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>DCM_ACTIVE</t>
+          <t>STRUCTURAL_DISCOUNT</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -6356,25 +6356,23 @@
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="H60" s="7" t="n">
-        <v>0.1928031370408962</v>
+        <v>0</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
           <t>0.015</t>
         </is>
       </c>
-      <c r="J60" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="J60" s="6" t="inlineStr"/>
       <c r="K60" s="6" t="inlineStr"/>
       <c r="L60" s="6" t="inlineStr"/>
       <c r="M60" s="3" t="n"/>
@@ -6382,12 +6380,12 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>JEGI.L</t>
+          <t>WWH.L</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>JPMorgan European Growth &amp; Incom</t>
+          <t>Worldwide Healthcare Trust</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -6397,7 +6395,7 @@
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>STRUCTURAL_DISCOUNT</t>
+          <t>DCM_ACTIVE</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -6407,23 +6405,25 @@
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="H61" s="7" t="n">
-        <v>0</v>
+        <v>0.1928031370408962</v>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
           <t>0.015</t>
         </is>
       </c>
-      <c r="J61" s="6" t="inlineStr"/>
+      <c r="J61" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="K61" s="6" t="inlineStr"/>
       <c r="L61" s="6" t="inlineStr"/>
       <c r="M61" s="3" t="n"/>
@@ -6431,21 +6431,23 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>HHI.L</t>
+          <t>BGCG.L</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Henderson High Income Trust</t>
+          <t>Baillie Gifford China Growth</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>BASE_QUIET</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="n">
-        <v/>
+          <t>RECENT_SELLOFF</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>DCM_ACTIVE</t>
+        </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
@@ -6454,38 +6456,38 @@
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="H62" s="7" t="n">
-        <v>0.0922810750531643</v>
+        <v>0.3815176411488281</v>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
           <t>0.015</t>
         </is>
       </c>
-      <c r="J62" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K62" s="6" t="inlineStr"/>
+      <c r="J62" s="6" t="inlineStr"/>
+      <c r="K62" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="L62" s="6" t="inlineStr"/>
       <c r="M62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>MUT.L</t>
+          <t>HHI.L</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Murray Income Trust</t>
+          <t>Henderson High Income Trust</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -6493,10 +6495,8 @@
           <t>BASE_QUIET</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>STRUCTURAL_DISCOUNT</t>
-        </is>
+      <c r="D63" s="7" t="n">
+        <v/>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
@@ -6505,16 +6505,16 @@
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="H63" s="7" t="n">
-        <v>0.2009620889852361</v>
+        <v>0.0922810750531643</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="J63" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K63" s="6" t="inlineStr"/>
       <c r="L63" s="6" t="inlineStr"/>
@@ -6531,12 +6531,12 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>NBPE.L</t>
+          <t>MUT.L</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>NB Private Equity Partners</t>
+          <t>Murray Income Trust</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
@@ -6546,17 +6546,17 @@
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>DCM_ACTIVE</t>
+          <t>STRUCTURAL_DISCOUNT</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>PRIVATE_EQUITY</t>
+          <t>LISTED_CLEAN</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="H64" s="7" t="n">
-        <v>0.4090923767905833</v>
+        <v>0.2009620889852361</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -6575,9 +6575,7 @@
       <c r="J64" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="K64" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="K64" s="6" t="inlineStr"/>
       <c r="L64" s="6" t="inlineStr"/>
       <c r="M64" s="3" t="n"/>
     </row>
@@ -6614,7 +6612,7 @@
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="H65" s="7" t="n">
@@ -6637,12 +6635,12 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>EDIN.L</t>
+          <t>NBPE.L</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Edinburgh Investment Trust</t>
+          <t>NB Private Equity Partners</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
@@ -6657,48 +6655,50 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>LISTED_CLEAN</t>
+          <t>PRIVATE_EQUITY</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="H66" s="7" t="n">
-        <v>0.2154558911269757</v>
+        <v>0.4090923767905833</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0.015</t>
         </is>
       </c>
       <c r="J66" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K66" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="K66" s="6" t="inlineStr"/>
       <c r="L66" s="6" t="inlineStr"/>
       <c r="M66" s="3" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>BGCG.L</t>
+          <t>EDIN.L</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Baillie Gifford China Growth</t>
+          <t>Edinburgh Investment Trust</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>RECENT_SELLOFF</t>
+          <t>BASE_QUIET</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -6713,26 +6713,26 @@
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="H67" s="7" t="n">
-        <v>0.3815176411488281</v>
+        <v>0.2154558911269757</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
           <t>0.014</t>
         </is>
       </c>
-      <c r="J67" s="6" t="inlineStr"/>
-      <c r="K67" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="J67" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" s="6" t="inlineStr"/>
       <c r="L67" s="6" t="inlineStr"/>
       <c r="M67" s="3" t="n"/>
     </row>
@@ -6786,10 +6786,14 @@
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>BPT.L</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr"/>
+          <t>BGUK.L</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>Baillie Gifford UK Growth</t>
+        </is>
+      </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
           <t>BASE_QUIET</t>
@@ -6800,32 +6804,34 @@
           <t>DCM_ACTIVE</t>
         </is>
       </c>
-      <c r="E69" s="7" t="n">
-        <v/>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>LISTED_CLEAN</t>
+        </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="H69" s="7" t="n">
-        <v>0.2122837508346098</v>
+        <v>0.4798668804260415</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0.014</t>
         </is>
       </c>
       <c r="J69" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L69" s="6" t="inlineStr"/>
       <c r="M69" s="3" t="n"/>
@@ -6833,12 +6839,12 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>BGUK.L</t>
+          <t>SST.L</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Baillie Gifford UK Growth</t>
+          <t>Scottish Oriental Smaller Compan</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
@@ -6858,27 +6864,27 @@
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="H70" s="7" t="n">
-        <v>0.4798668804260415</v>
+        <v>0.5602629114016884</v>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0.014</t>
         </is>
       </c>
       <c r="J70" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K70" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L70" s="6" t="inlineStr"/>
       <c r="M70" s="3" t="n"/>
@@ -6886,14 +6892,10 @@
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>AGT.L</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>AVI Global Trust</t>
-        </is>
-      </c>
+          <t>BPT.L</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr"/>
       <c r="C71" s="6" t="inlineStr">
         <is>
           <t>BASE_QUIET</t>
@@ -6904,14 +6906,12 @@
           <t>DCM_ACTIVE</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>LISTED_CLEAN</t>
-        </is>
+      <c r="E71" s="7" t="n">
+        <v/>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
@@ -6920,7 +6920,7 @@
         </is>
       </c>
       <c r="H71" s="7" t="n">
-        <v>0.2269320532093322</v>
+        <v>0.2122837508346098</v>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
@@ -6928,21 +6928,23 @@
         </is>
       </c>
       <c r="J71" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K71" s="6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K71" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="L71" s="6" t="inlineStr"/>
       <c r="M71" s="3" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>SST.L</t>
+          <t>AGT.L</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Scottish Oriental Smaller Compan</t>
+          <t>AVI Global Trust</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
@@ -6962,16 +6964,16 @@
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="H72" s="7" t="n">
-        <v>0.5602629114016884</v>
+        <v>0.2269320532093322</v>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
@@ -6981,9 +6983,7 @@
       <c r="J72" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="K72" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="K72" s="6" t="inlineStr"/>
       <c r="L72" s="6" t="inlineStr"/>
       <c r="M72" s="3" t="n"/>
     </row>
@@ -7139,12 +7139,12 @@
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>MRV.L</t>
+          <t>VNH.L</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Maven Renovar VCT</t>
+          <t>VietNam Holding</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
@@ -7154,33 +7154,35 @@
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>WIND_DOWN_LIKELY</t>
+          <t>DCM_ACTIVE</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>PRIVATE_EQUITY</t>
+          <t>LISTED_CLEAN</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="H76" s="7" t="n">
-        <v>0.1312943278823367</v>
+        <v>0.1686845811657413</v>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
           <t>0.011</t>
         </is>
       </c>
-      <c r="J76" s="6" t="inlineStr"/>
+      <c r="J76" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="K76" s="6" t="inlineStr"/>
       <c r="L76" s="6" t="inlineStr"/>
       <c r="M76" s="3" t="n"/>
@@ -7188,17 +7190,17 @@
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>VNH.L</t>
+          <t>JCGI.L</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>VietNam Holding</t>
+          <t>JPMorgan China Growth &amp; Income</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>BASE_QUIET</t>
+          <t>RECENT_SELLOFF</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -7213,67 +7215,67 @@
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="H77" s="7" t="n">
-        <v>0.1686845811657413</v>
+        <v>0.3162748879272431</v>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
           <t>0.011</t>
         </is>
       </c>
-      <c r="J77" s="7" t="n">
+      <c r="J77" s="6" t="inlineStr"/>
+      <c r="K77" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="K77" s="6" t="inlineStr"/>
       <c r="L77" s="6" t="inlineStr"/>
       <c r="M77" s="3" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>JCGI.L</t>
+          <t>MRV.L</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>JPMorgan China Growth &amp; Income</t>
+          <t>Maven Renovar VCT</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>RECENT_SELLOFF</t>
+          <t>BASE_QUIET</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>DCM_ACTIVE</t>
+          <t>WIND_DOWN_LIKELY</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>LISTED_CLEAN</t>
+          <t>PRIVATE_EQUITY</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="H78" s="7" t="n">
-        <v>0.3162748879272431</v>
+        <v>0.1312943278823367</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
@@ -7281,9 +7283,7 @@
         </is>
       </c>
       <c r="J78" s="6" t="inlineStr"/>
-      <c r="K78" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="K78" s="6" t="inlineStr"/>
       <c r="L78" s="6" t="inlineStr"/>
       <c r="M78" s="3" t="n"/>
     </row>
@@ -7588,14 +7588,10 @@
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>SOHO.L</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>Social Housing REIT</t>
-        </is>
-      </c>
+          <t>HLCL.L</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr"/>
       <c r="C85" s="6" t="inlineStr">
         <is>
           <t>BASE_QUIET</t>
@@ -7603,7 +7599,7 @@
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>STRATEGIC_REVIEW</t>
+          <t>STRUCTURAL_DISCOUNT</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -7613,36 +7609,40 @@
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="H85" s="7" t="n">
-        <v>0</v>
+        <v>0.2256952122044268</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
           <t>0.010</t>
         </is>
       </c>
-      <c r="J85" s="6" t="inlineStr"/>
-      <c r="K85" s="6" t="inlineStr"/>
+      <c r="J85" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="L85" s="6" t="inlineStr"/>
       <c r="M85" s="3" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>BPCR.L</t>
+          <t>SOHO.L</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>BioPharma Credit</t>
+          <t>Social Housing REIT</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
@@ -7652,22 +7652,22 @@
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>STRUCTURAL_DISCOUNT</t>
+          <t>STRATEGIC_REVIEW</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>DEBT_AMORTISING</t>
+          <t>PROPERTY_DCF</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="H86" s="7" t="n">
@@ -7686,10 +7686,14 @@
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>HLCL.L</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr"/>
+          <t>BPCR.L</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>BioPharma Credit</t>
+        </is>
+      </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
           <t>BASE_QUIET</t>
@@ -7702,33 +7706,29 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>PROPERTY_DCF</t>
+          <t>DEBT_AMORTISING</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="H87" s="7" t="n">
-        <v>0.2256952122044268</v>
+        <v>0</v>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
           <t>0.010</t>
         </is>
       </c>
-      <c r="J87" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K87" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="J87" s="6" t="inlineStr"/>
+      <c r="K87" s="6" t="inlineStr"/>
       <c r="L87" s="6" t="inlineStr"/>
       <c r="M87" s="3" t="n"/>
     </row>
@@ -8041,22 +8041,22 @@
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>FCSS.L</t>
+          <t>JCH.L</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Fidelity China Special Situation</t>
+          <t>JPMorgan Claverhouse</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>BASE_DECLINING</t>
+          <t>BASE_QUIET</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>DCM_ACTIVE</t>
+          <t>STRUCTURAL_DISCOUNT</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -8066,16 +8066,16 @@
       </c>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="H94" s="7" t="n">
-        <v>0.2314760651491938</v>
+        <v>0.0135770469722403</v>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
@@ -8083,21 +8083,19 @@
         </is>
       </c>
       <c r="J94" s="6" t="inlineStr"/>
-      <c r="K94" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="K94" s="6" t="inlineStr"/>
       <c r="L94" s="6" t="inlineStr"/>
       <c r="M94" s="3" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>JCH.L</t>
+          <t>CTY.L</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>JPMorgan Claverhouse</t>
+          <t>City of London Investment Trust</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
@@ -8107,7 +8105,7 @@
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>STRUCTURAL_DISCOUNT</t>
+          <t>DCM_ACTIVE</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -8117,20 +8115,20 @@
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="H95" s="7" t="n">
-        <v>0.0135770469722403</v>
+        <v>0</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.007</t>
         </is>
       </c>
       <c r="J95" s="6" t="inlineStr"/>
@@ -8141,17 +8139,17 @@
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>CTY.L</t>
+          <t>FCSS.L</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>City of London Investment Trust</t>
+          <t>Fidelity China Special Situation</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>BASE_QUIET</t>
+          <t>BASE_DECLINING</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -8166,16 +8164,16 @@
       </c>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="H96" s="7" t="n">
-        <v>0</v>
+        <v>0.2314760651491938</v>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
@@ -8183,7 +8181,9 @@
         </is>
       </c>
       <c r="J96" s="6" t="inlineStr"/>
-      <c r="K96" s="6" t="inlineStr"/>
+      <c r="K96" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="L96" s="6" t="inlineStr"/>
       <c r="M96" s="3" t="n"/>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="H97" s="7" t="n">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="H100" s="7" t="n">
@@ -8539,21 +8539,23 @@
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>BRFI.L</t>
+          <t>PNL.L</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>BlackRock Frontiers</t>
+          <t>Personal Assets Trust</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>BASE_QUIET</t>
-        </is>
-      </c>
-      <c r="D104" s="7" t="n">
-        <v/>
+          <t>BASE_ABSORBING</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>DCM_ACTIVE</t>
+        </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
@@ -8562,49 +8564,47 @@
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="H104" s="7" t="n">
-        <v>0.0599999999999999</v>
+        <v>0.2252130280066482</v>
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
           <t>0.005</t>
         </is>
       </c>
-      <c r="J104" s="6" t="inlineStr"/>
-      <c r="K104" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="J104" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K104" s="6" t="inlineStr"/>
       <c r="L104" s="6" t="inlineStr"/>
       <c r="M104" s="3" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>PNL.L</t>
+          <t>BRFI.L</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Personal Assets Trust</t>
+          <t>BlackRock Frontiers</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>BASE_ABSORBING</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>DCM_ACTIVE</t>
-        </is>
+          <t>BASE_QUIET</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="n">
+        <v/>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
@@ -8613,26 +8613,26 @@
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="H105" s="7" t="n">
-        <v>0.2252130280066482</v>
+        <v>0.0599999999999999</v>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
           <t>0.005</t>
         </is>
       </c>
-      <c r="J105" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K105" s="6" t="inlineStr"/>
+      <c r="J105" s="6" t="inlineStr"/>
+      <c r="K105" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="L105" s="6" t="inlineStr"/>
       <c r="M105" s="3" t="n"/>
     </row>
@@ -8892,12 +8892,12 @@
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>TRY.L</t>
+          <t>JIGI.L</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>TR Property Investment Trust</t>
+          <t>JPMorgan India Growth &amp; Income</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>PROPERTY_DCF</t>
+          <t>LISTED_CLEAN</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
@@ -8926,16 +8926,14 @@
         </is>
       </c>
       <c r="H111" s="7" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.1307125483170708</v>
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
           <t>0.004</t>
         </is>
       </c>
-      <c r="J111" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="J111" s="6" t="inlineStr"/>
       <c r="K111" s="6" t="inlineStr"/>
       <c r="L111" s="6" t="inlineStr"/>
       <c r="M111" s="3" t="n"/>
@@ -8943,12 +8941,12 @@
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>JIGI.L</t>
+          <t>TRY.L</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>JPMorgan India Growth &amp; Income</t>
+          <t>TR Property Investment Trust</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
@@ -8963,12 +8961,12 @@
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>LISTED_CLEAN</t>
+          <t>PROPERTY_DCF</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
@@ -8977,14 +8975,16 @@
         </is>
       </c>
       <c r="H112" s="7" t="n">
-        <v>0.1307125483170708</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
           <t>0.004</t>
         </is>
       </c>
-      <c r="J112" s="6" t="inlineStr"/>
+      <c r="J112" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="K112" s="6" t="inlineStr"/>
       <c r="L112" s="6" t="inlineStr"/>
       <c r="M112" s="3" t="n"/>
@@ -10467,7 +10467,7 @@
       </c>
       <c r="G142" s="6" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="H142" s="7" t="n">
@@ -10714,7 +10714,7 @@
       </c>
       <c r="G147" s="6" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="H147" s="7" t="n">
@@ -11041,12 +11041,12 @@
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>SDP.L</t>
+          <t>BGEU.L</t>
         </is>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>Schroder AsiaPacific Fund</t>
+          <t>Baillie Gifford European Growth</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>STRATEGIC_REVIEW</t>
+          <t>DCM_ACTIVE</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
@@ -11066,16 +11066,16 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="H154" s="7" t="n">
-        <v>0.1288212172292102</v>
+        <v>0.3803494462826214</v>
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
@@ -11083,19 +11083,21 @@
         </is>
       </c>
       <c r="J154" s="6" t="inlineStr"/>
-      <c r="K154" s="6" t="inlineStr"/>
+      <c r="K154" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="L154" s="6" t="inlineStr"/>
       <c r="M154" s="3" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>BGEU.L</t>
+          <t>SDP.L</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>Baillie Gifford European Growth</t>
+          <t>Schroder AsiaPacific Fund</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
@@ -11105,7 +11107,7 @@
       </c>
       <c r="D155" s="6" t="inlineStr">
         <is>
-          <t>DCM_ACTIVE</t>
+          <t>STRATEGIC_REVIEW</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr">
@@ -11115,16 +11117,16 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="G155" s="6" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="H155" s="7" t="n">
-        <v>0.3803494462826214</v>
+        <v>0.1288212172292102</v>
       </c>
       <c r="I155" s="6" t="inlineStr">
         <is>
@@ -11132,9 +11134,7 @@
         </is>
       </c>
       <c r="J155" s="6" t="inlineStr"/>
-      <c r="K155" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="K155" s="6" t="inlineStr"/>
       <c r="L155" s="6" t="inlineStr"/>
       <c r="M155" s="3" t="n"/>
     </row>
@@ -11326,7 +11326,7 @@
       </c>
       <c r="G159" s="6" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="H159" s="7" t="n">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="G161" s="6" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="H161" s="7" t="n">
@@ -11883,7 +11883,7 @@
       </c>
       <c r="G170" s="6" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="H170" s="7" t="n">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="G186" s="6" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-30.2%</t>
         </is>
       </c>
       <c r="H186" s="7" t="n">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="C14" s="3" t="n"/>
@@ -13454,7 +13454,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr"/>
@@ -13505,7 +13505,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr"/>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr"/>
@@ -13599,7 +13599,7 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr"/>
@@ -13648,7 +13648,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr"/>
@@ -13697,7 +13697,7 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr"/>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr"/>
@@ -14226,7 +14226,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr"/>
@@ -14275,7 +14275,7 @@
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr"/>
@@ -14371,7 +14371,7 @@
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr"/>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr"/>
@@ -14555,7 +14555,7 @@
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr"/>
@@ -14602,7 +14602,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr"/>
@@ -14739,7 +14739,7 @@
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr"/>
@@ -14825,7 +14825,7 @@
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr"/>
@@ -14872,7 +14872,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
@@ -15015,7 +15015,7 @@
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr"/>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="J6" s="3" t="n"/>
@@ -15667,7 +15667,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="J9" s="3" t="n"/>
@@ -15987,7 +15987,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="J17" s="3" t="n"/>
@@ -16147,7 +16147,7 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="J21" s="3" t="n"/>
@@ -16187,7 +16187,7 @@
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="J22" s="3" t="n"/>
@@ -16821,7 +16821,7 @@
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="J38" s="3" t="n"/>
@@ -17063,7 +17063,7 @@
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="J44" s="3" t="n"/>
@@ -17356,17 +17356,17 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>0.042</t>
         </is>
       </c>
       <c r="L6" s="3" t="n"/>
@@ -17688,17 +17688,17 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>0.041</t>
         </is>
       </c>
       <c r="L12" s="3" t="n"/>
@@ -17742,17 +17742,17 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>0.030</t>
         </is>
       </c>
       <c r="L13" s="3" t="n"/>
@@ -17908,12 +17908,12 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
@@ -18124,7 +18124,7 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>78.5%</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-30.2%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
@@ -18697,17 +18697,17 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>0.078</t>
         </is>
       </c>
       <c r="K5" s="3" t="n"/>
@@ -18799,17 +18799,17 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>0.041</t>
         </is>
       </c>
       <c r="K7" s="3" t="n"/>
@@ -19123,12 +19123,12 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>RCP.L</t>
+          <t>GSF.L</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>RIT Capital Partners</t>
+          <t>Gore Street Energy Storage</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -19138,35 +19138,35 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>BASE_ABSORBING</t>
+          <t>BASE_QUIET</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>+6.5pp</t>
+          <t>+13.1pp</t>
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0.2185306319462915</v>
+        <v>0.3199999999999999</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.031</t>
         </is>
       </c>
       <c r="K14" s="3" t="n"/>
@@ -19174,12 +19174,12 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>GSF.L</t>
+          <t>RCP.L</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Gore Street Energy Storage</t>
+          <t>RIT Capital Partners</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -19189,35 +19189,35 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>BASE_QUIET</t>
+          <t>BASE_ABSORBING</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>+13.1pp</t>
+          <t>+6.5pp</t>
         </is>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0.3199999999999999</v>
+        <v>0.2185306319462915</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>0.048</t>
         </is>
       </c>
       <c r="K15" s="3" t="n"/>
@@ -19225,12 +19225,12 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>SHIP.L</t>
+          <t>VOF.L</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Tufton Assets</t>
+          <t>VinaCapital Vietnam Opportunity</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -19245,20 +19245,20 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>-8.9pp</t>
+          <t>+6.0pp</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>0</v>
+        <v>0.3349769753593573</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -19268,7 +19268,7 @@
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.044</t>
         </is>
       </c>
       <c r="K16" s="3" t="n"/>
@@ -19276,12 +19276,12 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>ORIT.L</t>
+          <t>SHIP.L</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Octopus Renewables Infrastructure Trus</t>
+          <t>Tufton Assets</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -19296,30 +19296,30 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>+0.2pp</t>
+          <t>-8.9pp</t>
         </is>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0.1265034421998521</v>
+        <v>0</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>0.009</t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
@@ -19327,12 +19327,12 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>VOF.L</t>
+          <t>ORIT.L</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>VinaCapital Vietnam Opportunity</t>
+          <t>Octopus Renewables Infrastructure Trus</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -19347,30 +19347,30 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>+6.0pp</t>
+          <t>+0.2pp</t>
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>0.3349769753593573</v>
+        <v>0.1265034421998521</v>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>0.032</t>
         </is>
       </c>
       <c r="K18" s="3" t="n"/>
@@ -19458,12 +19458,12 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
@@ -19578,12 +19578,12 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>BBOX.L</t>
+          <t>JCGI.L</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Tritax Big Box REIT</t>
+          <t>JPMorgan China Growth &amp; Income</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -19593,21 +19593,25 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>BASE_QUIET</t>
+          <t>RECENT_SELLOFF</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>17.0%</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr"/>
+          <t>9.5%</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>+0.6pp</t>
+        </is>
+      </c>
       <c r="G23" s="7" t="n">
-        <v>0.1242033272178421</v>
+        <v>0.3162748879272431</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
@@ -19617,7 +19621,7 @@
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="K23" s="3" t="n"/>
@@ -19625,12 +19629,12 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>JCGI.L</t>
+          <t>BBOX.L</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>JPMorgan China Growth &amp; Income</t>
+          <t>Tritax Big Box REIT</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -19640,35 +19644,31 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>RECENT_SELLOFF</t>
+          <t>BASE_QUIET</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>9.5%</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>+0.6pp</t>
-        </is>
-      </c>
+          <t>17.0%</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr"/>
       <c r="G24" s="7" t="n">
-        <v>0.3162748879272431</v>
+        <v>0.1242033272178421</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.037</t>
         </is>
       </c>
       <c r="K24" s="3" t="n"/>
@@ -19676,50 +19676,50 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>FGEN.L</t>
+          <t>BRSC.L</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Foresight Environmental Infrastructure</t>
+          <t>BlackRock Smaller Companies</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>STRATEGIC_REVIEW</t>
+          <t>DCM_ACTIVE</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>POST_RERATING</t>
+          <t>RECENT_SELLOFF</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>-10.8pp</t>
+          <t>+3.0pp</t>
         </is>
       </c>
       <c r="G25" s="7" t="n">
-        <v>0.0799999999999999</v>
+        <v>0.5335882862438193</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.019</t>
         </is>
       </c>
       <c r="K25" s="3" t="n"/>
@@ -19727,50 +19727,50 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>BRSC.L</t>
+          <t>FGEN.L</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>BlackRock Smaller Companies</t>
+          <t>Foresight Environmental Infrastructure</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>DCM_ACTIVE</t>
+          <t>STRATEGIC_REVIEW</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>RECENT_SELLOFF</t>
+          <t>POST_RERATING</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>+3.0pp</t>
+          <t>-10.8pp</t>
         </is>
       </c>
       <c r="G26" s="7" t="n">
-        <v>0.5335882862438193</v>
+        <v>0.0799999999999999</v>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="K26" s="3" t="n"/>
@@ -19811,12 +19811,12 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
@@ -19913,12 +19913,12 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
@@ -19931,12 +19931,12 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>SCF.L</t>
+          <t>BGUK.L</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Schroder Income Growth Fund</t>
+          <t>Baillie Gifford UK Growth</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -19951,30 +19951,30 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>+0.4pp</t>
+          <t>+0.0pp</t>
         </is>
       </c>
       <c r="G30" s="7" t="n">
-        <v>0.262630640191182</v>
+        <v>0.4798668804260415</v>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>0.014</t>
         </is>
       </c>
       <c r="K30" s="3" t="n"/>
@@ -19982,12 +19982,12 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>MRCH.L</t>
+          <t>SCF.L</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Merchants Trust</t>
+          <t>Schroder Income Growth Fund</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -20002,30 +20002,30 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>+0.2pp</t>
+          <t>+0.4pp</t>
         </is>
       </c>
       <c r="G31" s="7" t="n">
-        <v>0.0964546321911891</v>
+        <v>0.262630640191182</v>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>0.016</t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
@@ -20033,12 +20033,12 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>BGUK.L</t>
+          <t>MRCH.L</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Baillie Gifford UK Growth</t>
+          <t>Merchants Trust</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -20053,30 +20053,30 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>+0.0pp</t>
+          <t>+0.2pp</t>
         </is>
       </c>
       <c r="G32" s="7" t="n">
-        <v>0.4798668804260415</v>
+        <v>0.0964546321911891</v>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0.018</t>
         </is>
       </c>
       <c r="K32" s="3" t="n"/>
@@ -20186,12 +20186,12 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>MRC.L</t>
+          <t>JFJ.L</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Mercantile Investment Trust</t>
+          <t>JPMorgan Japanese</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -20206,20 +20206,20 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>+0.5pp</t>
+          <t>+0.8pp</t>
         </is>
       </c>
       <c r="G35" s="7" t="n">
-        <v>0.1463023814482843</v>
+        <v>0.2731981275982885</v>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>0.036</t>
         </is>
       </c>
       <c r="K35" s="3" t="n"/>
@@ -20237,12 +20237,12 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>IBT.L</t>
+          <t>BGCG.L</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>International Biotechnology</t>
+          <t>Baillie Gifford China Growth</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -20257,7 +20257,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -20266,11 +20266,11 @@
         </is>
       </c>
       <c r="G36" s="7" t="n">
-        <v>0.0064795945371216</v>
+        <v>0.3815176411488281</v>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
@@ -20280,7 +20280,7 @@
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0.015</t>
         </is>
       </c>
       <c r="K36" s="3" t="n"/>
@@ -20288,12 +20288,12 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>ASL.L</t>
+          <t>MRC.L</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Aberforth Smaller Companies</t>
+          <t>Mercantile Investment Trust</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -20303,35 +20303,35 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>RECENT_SELLOFF</t>
+          <t>BASE_ABSORBING</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>+0.3pp</t>
+          <t>+0.5pp</t>
         </is>
       </c>
       <c r="G37" s="7" t="n">
-        <v>0.1944571913826297</v>
+        <v>0.1463023814482843</v>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0.043</t>
         </is>
       </c>
       <c r="K37" s="3" t="n"/>
@@ -20339,12 +20339,12 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>JFJ.L</t>
+          <t>IBT.L</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>JPMorgan Japanese</t>
+          <t>International Biotechnology</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -20354,35 +20354,35 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>BASE_ABSORBING</t>
+          <t>RECENT_SELLOFF</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>+0.8pp</t>
+          <t>+0.0pp</t>
         </is>
       </c>
       <c r="G38" s="7" t="n">
-        <v>0.2731981275982885</v>
+        <v>0.0064795945371216</v>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="K38" s="3" t="n"/>
@@ -20390,12 +20390,12 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>BGCG.L</t>
+          <t>ASL.L</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Baillie Gifford China Growth</t>
+          <t>Aberforth Smaller Companies</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -20410,30 +20410,30 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>+0.0pp</t>
+          <t>+0.3pp</t>
         </is>
       </c>
       <c r="G39" s="7" t="n">
-        <v>0.3815176411488281</v>
+        <v>0.1944571913826297</v>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0.013</t>
         </is>
       </c>
       <c r="K39" s="3" t="n"/>
@@ -20492,12 +20492,12 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>EDIN.L</t>
+          <t>VEIL.L</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Edinburgh Investment Trust</t>
+          <t>Vietnam Enterprise Investments</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -20512,20 +20512,20 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>+3.2pp</t>
+          <t>+0.0pp</t>
         </is>
       </c>
       <c r="G41" s="7" t="n">
-        <v>0.2154558911269757</v>
+        <v>0.1357381665965281</v>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="K41" s="3" t="n"/>
@@ -20543,12 +20543,12 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>VEIL.L</t>
+          <t>CTPE.L</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Vietnam Enterprise Investments</t>
+          <t>CT Private Equity Trust</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -20563,30 +20563,30 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>+0.0pp</t>
+          <t>-0.7pp</t>
         </is>
       </c>
       <c r="G42" s="7" t="n">
-        <v>0.1357381665965281</v>
+        <v>0.1378966069627241</v>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0.023</t>
         </is>
       </c>
       <c r="K42" s="3" t="n"/>
@@ -20594,12 +20594,12 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>CTPE.L</t>
+          <t>HSL.L</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>CT Private Equity Trust</t>
+          <t>Henderson Smaller Companies</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -20614,20 +20614,20 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>-0.7pp</t>
+          <t>-0.6pp</t>
         </is>
       </c>
       <c r="G43" s="7" t="n">
-        <v>0.1378966069627241</v>
+        <v>0.1254725434583484</v>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -20637,7 +20637,7 @@
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>0.022</t>
         </is>
       </c>
       <c r="K43" s="3" t="n"/>
@@ -20645,12 +20645,12 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>HSL.L</t>
+          <t>INPP.L</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Henderson Smaller Companies</t>
+          <t>International Public Partnerships</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -20665,20 +20665,20 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>-0.6pp</t>
+          <t>-4.8pp</t>
         </is>
       </c>
       <c r="G44" s="7" t="n">
-        <v>0.1254725434583484</v>
+        <v>0.2388227823699436</v>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
@@ -20688,7 +20688,7 @@
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>0.019</t>
         </is>
       </c>
       <c r="K44" s="3" t="n"/>
@@ -20696,12 +20696,12 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>INPP.L</t>
+          <t>EDIN.L</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>International Public Partnerships</t>
+          <t>Edinburgh Investment Trust</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -20716,20 +20716,20 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>-4.8pp</t>
+          <t>+3.2pp</t>
         </is>
       </c>
       <c r="G45" s="7" t="n">
-        <v>0.2388227823699436</v>
+        <v>0.2154558911269757</v>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
@@ -20739,7 +20739,7 @@
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.014</t>
         </is>
       </c>
       <c r="K45" s="3" t="n"/>
@@ -20798,12 +20798,12 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>SAIN.L</t>
+          <t>SCP.L</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Scottish American</t>
+          <t>Schroder UK Mid Cap Fund</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -20818,20 +20818,20 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>+5.5pp</t>
+          <t>-4.1pp</t>
         </is>
       </c>
       <c r="G47" s="7" t="n">
-        <v>0.1420070683839654</v>
+        <v>0.417357717103107</v>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
@@ -20841,7 +20841,7 @@
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>0.015</t>
         </is>
       </c>
       <c r="K47" s="3" t="n"/>
@@ -20849,12 +20849,12 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>SCP.L</t>
+          <t>SAIN.L</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Schroder UK Mid Cap Fund</t>
+          <t>Scottish American</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -20869,30 +20869,30 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>-4.1pp</t>
+          <t>+5.5pp</t>
         </is>
       </c>
       <c r="G48" s="7" t="n">
-        <v>0.417357717103107</v>
+        <v>0.1420070683839654</v>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>0.017</t>
         </is>
       </c>
       <c r="K48" s="3" t="n"/>
@@ -21002,12 +21002,12 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>FCSS.L</t>
+          <t>FEV.L</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Fidelity China Special Situations</t>
+          <t>Fidelity European Trust</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -21017,25 +21017,25 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>BASE_DECLINING</t>
+          <t>BASE_ABSORBING</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>-2.1pp</t>
+          <t>-0.3pp</t>
         </is>
       </c>
       <c r="G51" s="7" t="n">
-        <v>0.2314760651491938</v>
+        <v>0.2824236703131528</v>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
@@ -21045,7 +21045,7 @@
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.033</t>
         </is>
       </c>
       <c r="K51" s="3" t="n"/>
@@ -21053,12 +21053,12 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>FEV.L</t>
+          <t>NBPE.L</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Fidelity European Trust</t>
+          <t>NB Private Equity Partners</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -21068,35 +21068,35 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>BASE_ABSORBING</t>
+          <t>BASE_QUIET</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>-0.3pp</t>
+          <t>-1.8pp</t>
         </is>
       </c>
       <c r="G52" s="7" t="n">
-        <v>0.2824236703131528</v>
+        <v>0.4090923767905833</v>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>0.015</t>
         </is>
       </c>
       <c r="K52" s="3" t="n"/>
@@ -21104,12 +21104,12 @@
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>NBPE.L</t>
+          <t>PPET.L</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>NB Private Equity Partners</t>
+          <t>Patria Private Equity</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -21124,20 +21124,20 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>-1.8pp</t>
+          <t>+0.0pp</t>
         </is>
       </c>
       <c r="G53" s="7" t="n">
-        <v>0.4090923767905833</v>
+        <v>0.2630125523111781</v>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
@@ -21147,7 +21147,7 @@
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>0.017</t>
         </is>
       </c>
       <c r="K53" s="3" t="n"/>
@@ -21155,12 +21155,12 @@
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>PPET.L</t>
+          <t>FCSS.L</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Patria Private Equity</t>
+          <t>Fidelity China Special Situations</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
@@ -21170,35 +21170,35 @@
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>BASE_QUIET</t>
+          <t>BASE_DECLINING</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>+0.0pp</t>
+          <t>-2.1pp</t>
         </is>
       </c>
       <c r="G54" s="9" t="n">
-        <v>0.2630125523111781</v>
+        <v>0.2314760651491938</v>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>0.007</t>
         </is>
       </c>
       <c r="K54" s="3" t="n"/>
@@ -21454,12 +21454,12 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>0.078</t>
         </is>
       </c>
       <c r="J6" s="3" t="n"/>
@@ -21789,17 +21789,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>MRC.L</t>
+          <t>VOF.L</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Mercantile Investment Trust</t>
+          <t>VinaCapital Vietnam Opportunity</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>BASE_ABSORBING</t>
+          <t>BASE_QUIET</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -21809,12 +21809,12 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="G14" s="7" t="n">
@@ -21822,12 +21822,12 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>0.044</t>
         </is>
       </c>
       <c r="J14" s="3" t="n"/>
@@ -21835,17 +21835,17 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>VOF.L</t>
+          <t>MRC.L</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>VinaCapital Vietnam Opportunity</t>
+          <t>Mercantile Investment Trust</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>BASE_QUIET</t>
+          <t>BASE_ABSORBING</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -21855,12 +21855,12 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="G15" s="7" t="n">
@@ -21868,12 +21868,12 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>0.043</t>
         </is>
       </c>
       <c r="J15" s="3" t="n"/>
@@ -21914,12 +21914,12 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>0.041</t>
         </is>
       </c>
       <c r="J16" s="3" t="n"/>
@@ -22144,12 +22144,12 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>0.036</t>
         </is>
       </c>
       <c r="J21" s="3" t="n"/>
@@ -22249,12 +22249,12 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>SEQI.L</t>
+          <t>TFIF.L</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Sequoia Economic Infrastructure Income</t>
+          <t>TwentyFour Income Fund</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -22264,17 +22264,17 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>DCM_ACTIVE</t>
+          <t>STRUCTURAL_DISCOUNT</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G24" s="7" t="n">
@@ -22282,7 +22282,7 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
@@ -22295,12 +22295,12 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>TFIF.L</t>
+          <t>SEQI.L</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>TwentyFour Income Fund</t>
+          <t>Sequoia Economic Infrastructure Income</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -22310,17 +22310,17 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>STRUCTURAL_DISCOUNT</t>
+          <t>DCM_ACTIVE</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="G25" s="7" t="n">
@@ -22328,7 +22328,7 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -22433,17 +22433,17 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>ALW.L</t>
+          <t>GSF.L</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Alliance Witan</t>
+          <t>Gore Street Energy Storage</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>BASE_ABSORBING</t>
+          <t>BASE_QUIET</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -22453,20 +22453,20 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="G28" s="7" t="n">
-        <v>208</v>
+        <v>131</v>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
@@ -22479,17 +22479,17 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>GSF.L</t>
+          <t>ALW.L</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Gore Street Energy Storage</t>
+          <t>Alliance Witan</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>BASE_QUIET</t>
+          <t>BASE_ABSORBING</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -22499,20 +22499,20 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="G29" s="7" t="n">
-        <v>131</v>
+        <v>208</v>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
@@ -22571,12 +22571,12 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>CVCG.L</t>
+          <t>CTHT.L</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>CVC Income &amp; Growth</t>
+          <t>CT Healthcare Trust</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -22586,17 +22586,17 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>STRUCTURAL_DISCOUNT</t>
+          <t>WIND_DOWN_LIKELY</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="G31" s="7" t="n">
@@ -22604,7 +22604,7 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
@@ -22617,12 +22617,12 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>CTHT.L</t>
+          <t>CVCG.L</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>CT Healthcare Trust</t>
+          <t>CVC Income &amp; Growth</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -22632,17 +22632,17 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>WIND_DOWN_LIKELY</t>
+          <t>STRUCTURAL_DISCOUNT</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G32" s="7" t="n">
@@ -22650,12 +22650,12 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>0.030</t>
         </is>
       </c>
       <c r="J32" s="3" t="n"/>
@@ -22788,7 +22788,7 @@
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
@@ -23455,7 +23455,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -23465,7 +23465,7 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -23526,47 +23526,47 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>CHRY.L</t>
+          <t>GCP.L</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Chrysalis Investments</t>
+          <t>GCP Infrastructure Investments</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>RETURN_OF_CAPITAL_LIVE</t>
+          <t>STRATEGIC_REVIEW</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>PRIVATE_EQUITY</t>
+          <t>DEBT_AMORTISING</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">disc 46%; return of capital live; insider buys ×3 </t>
+          <t>strategic review; activist ×1; yield 8.9%; 21m int</t>
         </is>
       </c>
       <c r="J8" s="3" t="n"/>
@@ -23574,33 +23574,37 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>GSEO.L</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr"/>
+          <t>CHRY.L</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Chrysalis Investments</t>
+        </is>
+      </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>WIND_DOWN_COMMITTED</t>
+          <t>RETURN_OF_CAPITAL_LIVE</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>RENEWABLES_DCF</t>
+          <t>PRIVATE_EQUITY</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -23610,7 +23614,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>disc 35%; wind down committed; 23m into workout</t>
+          <t xml:space="preserve">disc 46%; return of capital live; insider buys ×3 </t>
         </is>
       </c>
       <c r="J9" s="3" t="n"/>
@@ -23618,47 +23622,43 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>GCP.L</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>GCP Infrastructure Investments</t>
-        </is>
-      </c>
+          <t>GSEO.L</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr"/>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>STRATEGIC_REVIEW</t>
+          <t>WIND_DOWN_COMMITTED</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>DEBT_AMORTISING</t>
+          <t>RENEWABLES_DCF</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>strategic review; activist ×1; yield 8.9%; 21m int</t>
+          <t>disc 35%; wind down committed; 23m into workout</t>
         </is>
       </c>
       <c r="J10" s="3" t="n"/>
@@ -23739,7 +23739,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -23749,7 +23749,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -24142,12 +24142,12 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>RCP.L</t>
+          <t>GSF.L</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>RIT Capital Partners</t>
+          <t>Gore Street Energy Storage</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -24157,17 +24157,17 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>LISTED_CLEAN</t>
+          <t>RENEWABLES_DCF</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
@@ -24177,12 +24177,12 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>dcm active; base absorbing</t>
+          <t>disc 43%; dcm active (auto-promoted by discount_st</t>
         </is>
       </c>
       <c r="J21" s="3" t="n"/>
@@ -24190,12 +24190,12 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>GSF.L</t>
+          <t>RCP.L</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Gore Street Energy Storage</t>
+          <t>RIT Capital Partners</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -24205,17 +24205,17 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>RENEWABLES_DCF</t>
+          <t>LISTED_CLEAN</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -24225,12 +24225,12 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>disc 43%; dcm active (auto-promoted by discount_st</t>
+          <t>dcm active; base absorbing</t>
         </is>
       </c>
       <c r="J22" s="3" t="n"/>
@@ -24238,12 +24238,12 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>SHIP.L</t>
+          <t>VOF.L</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Tufton Assets</t>
+          <t>VinaCapital Vietnam Opportunity</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -24253,17 +24253,17 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>REAL_ASSET_OBSERVABLE</t>
+          <t>LISTED_CLEAN</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>dcm active (auto-promoted by discount_stretch); yi</t>
+          <t>dcm active; resolution 0.33; activist ×1; material</t>
         </is>
       </c>
       <c r="J23" s="3" t="n"/>
@@ -24286,12 +24286,12 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>ORIT.L</t>
+          <t>SHIP.L</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Octopus Renewables Infrastructure Tr</t>
+          <t>Tufton Assets</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -24301,17 +24301,17 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>RENEWABLES_DCF</t>
+          <t>REAL_ASSET_OBSERVABLE</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
@@ -24321,12 +24321,12 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>disc 30%; dcm active; yield 9.5%</t>
+          <t>dcm active (auto-promoted by discount_stretch); yi</t>
         </is>
       </c>
       <c r="J24" s="3" t="n"/>
@@ -24334,12 +24334,12 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>VOF.L</t>
+          <t>ORIT.L</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>VinaCapital Vietnam Opportunity</t>
+          <t>Octopus Renewables Infrastructure Tr</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -24349,17 +24349,17 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>LISTED_CLEAN</t>
+          <t>RENEWABLES_DCF</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -24369,12 +24369,12 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>dcm active; resolution 0.33; activist ×1; material</t>
+          <t>disc 30%; dcm active; yield 9.5%</t>
         </is>
       </c>
       <c r="J25" s="3" t="n"/>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -24465,7 +24465,7 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
@@ -24478,17 +24478,17 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>PSH.L</t>
+          <t>BRLA.L</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Pershing Square Holdings</t>
+          <t>BlackRock Latin American</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>DCM_ACTIVE</t>
+          <t>WIND_DOWN_LIKELY</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -24498,27 +24498,27 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>disc 34%; dcm active</t>
+          <t xml:space="preserve">wind down likely (auto-promoted by rns); activist </t>
         </is>
       </c>
       <c r="J28" s="3" t="n"/>
@@ -24526,17 +24526,17 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>BRLA.L</t>
+          <t>PSH.L</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>BlackRock Latin American</t>
+          <t>Pershing Square Holdings</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>WIND_DOWN_LIKELY</t>
+          <t>DCM_ACTIVE</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -24546,27 +24546,27 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind down likely (auto-promoted by rns); activist </t>
+          <t>disc 34%; dcm active</t>
         </is>
       </c>
       <c r="J29" s="3" t="n"/>
@@ -24574,47 +24574,47 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>UKW.L</t>
+          <t>CTHT.L</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Greencoat UK Wind</t>
+          <t>CT Healthcare Trust</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>DCM_ACTIVE</t>
+          <t>WIND_DOWN_LIKELY</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>RENEWABLES_DCF</t>
+          <t>LISTED_CLEAN</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>dcm active; insider buys ×2 (£691k); base absorbin</t>
+          <t>wind down likely (auto-promoted by rns); resolutio</t>
         </is>
       </c>
       <c r="J30" s="3" t="n"/>
@@ -24622,47 +24622,47 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>CTHT.L</t>
+          <t>UKW.L</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>CT Healthcare Trust</t>
+          <t>Greencoat UK Wind</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>WIND_DOWN_LIKELY</t>
+          <t>DCM_ACTIVE</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>LISTED_CLEAN</t>
+          <t>RENEWABLES_DCF</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>wind down likely (auto-promoted by rns); resolutio</t>
+          <t>dcm active; insider buys ×2 (£691k); base absorbin</t>
         </is>
       </c>
       <c r="J31" s="3" t="n"/>
@@ -24670,12 +24670,12 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>BBOX.L</t>
+          <t>JCGI.L</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Tritax Big Box REIT</t>
+          <t>JPMorgan China Growth &amp; Income</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -24690,12 +24690,12 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
@@ -24710,7 +24710,7 @@
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>dcm active; insider buys ×2 (£2k); yield 5.3%</t>
+          <t>dcm active; resolution 0.32; activist ×1; material</t>
         </is>
       </c>
       <c r="J32" s="3" t="n"/>
@@ -24718,12 +24718,12 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>JCGI.L</t>
+          <t>BBOX.L</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>JPMorgan China Growth &amp; Income</t>
+          <t>Tritax Big Box REIT</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -24738,12 +24738,12 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
@@ -24753,12 +24753,12 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>dcm active; resolution 0.32; activist ×1; material</t>
+          <t>dcm active; insider buys ×2 (£2k); yield 5.3%</t>
         </is>
       </c>
       <c r="J33" s="3" t="n"/>
@@ -24766,47 +24766,47 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>FGEN.L</t>
+          <t>BRSC.L</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Foresight Environmental Infrastructu</t>
+          <t>BlackRock Smaller Companies</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>STRATEGIC_REVIEW</t>
+          <t>DCM_ACTIVE</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>RENEWABLES_DCF</t>
+          <t>LISTED_CLEAN</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>strategic review; yield 9.3%; 22m into workout</t>
+          <t>dcm active; resolution 0.53; activist ×2; material</t>
         </is>
       </c>
       <c r="J34" s="3" t="n"/>
@@ -24814,47 +24814,47 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>BRSC.L</t>
+          <t>FGEN.L</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>BlackRock Smaller Companies</t>
+          <t>Foresight Environmental Infrastructu</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>DCM_ACTIVE</t>
+          <t>STRATEGIC_REVIEW</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>LISTED_CLEAN</t>
+          <t>RENEWABLES_DCF</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>dcm active; resolution 0.53; activist ×2; material</t>
+          <t>strategic review; yield 9.3%; 22m into workout</t>
         </is>
       </c>
       <c r="J35" s="3" t="n"/>
@@ -24887,7 +24887,7 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
@@ -24897,7 +24897,7 @@
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
@@ -24983,7 +24983,7 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
@@ -24993,7 +24993,7 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
@@ -25006,47 +25006,47 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>JARA.L</t>
+          <t>BGUK.L</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>JPMorgan Global Core Real Assets</t>
+          <t>Baillie Gifford UK Growth</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>WIND_DOWN_COMMITTED</t>
+          <t>DCM_ACTIVE</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>INFRA_DCF</t>
+          <t>LISTED_CLEAN</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>wind down committed; yield 5.4%</t>
+          <t>dcm active; resolution 0.48; activist ×5</t>
         </is>
       </c>
       <c r="J39" s="3" t="n"/>
@@ -25054,37 +25054,37 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>SCF.L</t>
+          <t>JARA.L</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Schroder Income Growth Fund</t>
+          <t>JPMorgan Global Core Real Assets</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>DCM_ACTIVE</t>
+          <t>WIND_DOWN_COMMITTED</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>LISTED_CLEAN</t>
+          <t>INFRA_DCF</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
@@ -25094,7 +25094,7 @@
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>dcm active; insider buys ×3 (£6k)</t>
+          <t>wind down committed; yield 5.4%</t>
         </is>
       </c>
       <c r="J40" s="3" t="n"/>
@@ -25102,12 +25102,12 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>MRCH.L</t>
+          <t>SCF.L</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Merchants Trust</t>
+          <t>Schroder Income Growth Fund</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -25122,12 +25122,12 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
@@ -25137,12 +25137,12 @@
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>dcm active (auto-promoted by discount_stretch)</t>
+          <t>dcm active; insider buys ×3 (£6k)</t>
         </is>
       </c>
       <c r="J41" s="3" t="n"/>
@@ -25150,12 +25150,12 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>BGUK.L</t>
+          <t>MRCH.L</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Baillie Gifford UK Growth</t>
+          <t>Merchants Trust</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -25170,12 +25170,12 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
@@ -25185,12 +25185,12 @@
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>dcm active; resolution 0.48; activist ×5</t>
+          <t>dcm active (auto-promoted by discount_stretch)</t>
         </is>
       </c>
       <c r="J42" s="3" t="n"/>
@@ -25653,7 +25653,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="H10" s="3" t="n"/>
